--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="24720" yWindow="9020" windowWidth="57000" windowHeight="23480" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="papers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chapters" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dissertations" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="talks" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="courses" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="posters" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="papers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="chapters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="dissertations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="talks" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="courses" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="posters" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -590,6 +590,11 @@
           <t>data_link</t>
         </is>
       </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="68" customHeight="1">
       <c r="A2" t="inlineStr">
@@ -667,16 +672,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>bioRxiv</t>
+          <t>Communications Biology</t>
         </is>
       </c>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>10.64898/2026.04.30.722005v1</t>
-        </is>
-      </c>
+      <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>https://www.biorxiv.org/content/10.64898/2026.04.30.722005v1</t>
@@ -690,6 +691,11 @@
       <c r="L3" s="3" t="inlineStr">
         <is>
           <t>https://db.humanconnectome.org</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>In press</t>
         </is>
       </c>
     </row>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -595,6 +595,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>cv_note</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>author_roles</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="68" customHeight="1">
       <c r="A2" t="inlineStr">
@@ -731,9 +741,6 @@
       <c r="G4" t="n">
         <v>17</v>
       </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>2055</t>
@@ -808,70 +815,59 @@
       </c>
     </row>
     <row r="6" ht="51" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>high-level-cognition-pnas.png</t>
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>sciam-past.png</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Owen LLW, Manning JR</t>
+          <t>Manning JR</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>High-level cognition is supported by information-rich but compressible brain activity patterns</t>
+          <t>Why we're so preoccupied by the past</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>https://www.pnas.org/doi/10.1073/pnas.2400082121</t>
+          <t>https://www.scientificamerican.com/article/why-were-so-preoccupied-by-the-past/</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Proceedings of the National Academy of Sciences, USA</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>121</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>e2400082121</t>
-        </is>
-      </c>
+          <t>Scientific American</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+      <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>https://biorxiv.org/cgi/content/short/2023.03.17.533152v1</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/ContextLab/pca_paper</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/ContextLab/pca_paper</t>
+          <t>https://www.scientificamerican.com/article/why-were-so-preoccupied-by-the-past/</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Online</t>
         </is>
       </c>
     </row>
     <row r="7" ht="51" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>psychological-arrow-time.png</t>
+          <t>high-level-cognition-pnas.png</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Xu X, Zhu Z, Manning JR</t>
+          <t>Owen LLW, Manning JR</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
@@ -879,55 +875,55 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>The psychological arrow of time drives temporal asymmetries in inferring unobserved past and future events</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nature.com/articles/s41467-024-52627-5</t>
+          <t>High-level cognition is supported by information-rich but compressible brain activity patterns</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pnas.org/doi/10.1073/pnas.2400082121</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Nature Communications</t>
+          <t>Proceedings of the National Academy of Sciences, USA</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>8502</v>
+        <v>35</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>doi.org/10.1038/s41467-024-52627-5</t>
+          <t>e2400082121</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>https://psyarxiv.com/yp2qu</t>
+          <t>https://biorxiv.org/cgi/content/short/2023.03.17.533152v1</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/prediction-retrodiction-paper</t>
+          <t>https://github.com/ContextLab/pca_paper</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/prediction-retrodiction-paper</t>
+          <t>https://github.com/ContextLab/pca_paper</t>
         </is>
       </c>
     </row>
     <row r="8" ht="51" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>davos.png</t>
+          <t>psychological-arrow-time.png</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Fitzpatrick PC, Manning JR</t>
+          <t>Xu X, Zhu Z, Zheng X, Manning JR</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
@@ -935,99 +931,104 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Davos: a Python "smuggler" for constructing lightweight reproducible notebooks</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S2352711023003102</t>
+          <t>Temporal asymmetries in inferring unobserved past and future events</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/articles/s41467-024-52627-5</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>SoftwareX</t>
+          <t>Nature Communications</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n">
-        <v>101614</v>
+        <v>8502</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S2352711023003102/pdfft</t>
+          <t>https://psyarxiv.com/yp2qu</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/davos</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="n"/>
+          <t>https://github.com/ContextLab/prediction-retrodiction-paper</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/ContextLab/prediction-retrodiction-paper</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Zhu Z: none; Zheng X: none</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="51" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>people-relationships.png</t>
+          <t>davos.png</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Jolly E, Sadhukha S, Iqbal M, Molani Z, Walsh T, Manning JR, Chang LJ</t>
+          <t>Fitzpatrick PC, Manning JR</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>People are represented and remembered through their relationships with others</t>
+          <t>Davos: a Python package "smuggler" for constructing lightweight reproducible notebooks</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>https://psyarxiv.com/bw9r2/</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S2352711023003102</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>PsyArXiv</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="n"/>
+          <t>SoftwareX</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>10.31234/osf.io/bw9r2</t>
-        </is>
+      <c r="I9" s="3" t="n">
+        <v>101614</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>https://psyarxiv.com/bw9r2/</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S2352711023003102/pdfft</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ejolly/social_mem</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/ejolly/social_mem</t>
-        </is>
-      </c>
+          <t>https://github.com/ContextLab/davos</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="n"/>
     </row>
     <row r="10" ht="51" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>ZimaEtAl19-34.png</t>
+          <t>people-relationships.png</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Ziman K, Lee MR, Martinez AR, Adner ED, Manning JR</t>
+          <t>Jolly E, Sadhukha S, Iqbal M, Molani Z, Walsh T, Manning JR, Chang LJ</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
@@ -1035,12 +1036,12 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Category-based and location-based volitional covert attention affect memory at different timescales</t>
+          <t>People are represented and remembered through their relationships with others</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>https://psyarxiv.com/2ps6e/</t>
+          <t>https://psyarxiv.com/bw9r2/</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1052,34 +1053,39 @@
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>10.31234/osf.io/2ps6e</t>
+          <t>10.31234/osf.io/bw9r2</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>https://psyarxiv.com/2ps6e/</t>
+          <t>https://psyarxiv.com/bw9r2/</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/attention-memory-task</t>
+          <t>https://github.com/ejolly/social_mem</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/attention-memory-task</t>
+          <t>https://github.com/ejolly/social_mem</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Jolly E: postdoc; Sadhukha S: grad; Iqbal M: undergrad; Molani Z: undergrad; Walsh T: undergrad</t>
         </is>
       </c>
     </row>
     <row r="11" ht="187" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>feature-order-recall.png</t>
+          <t>ZimaEtAl19-34.png</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Manning JR, Whitaker EC, Fitzpatrick PC, Lee MR, Frantz AM, Bollinger BJ, Romanova D, Field CE, Heusser AC</t>
+          <t>Ziman K, Lee MR, Martinez AR, Adner ED, Manning JR</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
@@ -1087,12 +1093,12 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Feature and order manipulations in a free recall task affect memory for current and future lists</t>
+          <t>Category-based and location-based volitional covert attention are mediated by different mechanisms and affect memory at different timescales</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>https://psyarxiv.com/erzfp</t>
+          <t>https://psyarxiv.com/2ps6e/</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1104,90 +1110,91 @@
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>10.31234/osf.io/erzfp</t>
+          <t>10.31234/osf.io/2ps6e</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>https://psyarxiv.com/erzfp</t>
+          <t>https://psyarxiv.com/2ps6e/</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/FRFR-analyses</t>
+          <t>https://github.com/ContextLab/attention-memory-task</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/FRFR-analyses</t>
+          <t>https://github.com/ContextLab/attention-memory-task</t>
         </is>
       </c>
     </row>
     <row r="12" ht="68" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>fitness-tracking.png</t>
+          <t>feature-order-recall.png</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Manning JR, Notaro GM, Chen E, Fitzpatrick PC</t>
+          <t>Manning JR, Whitaker EC, Fitzpatrick PC, Lee MR, Frantz AM, Bollinger BJ, Romanova D, Field CE, Heusser AC</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Fitness tracking reveals task-specific associations between memory, mental health, and exercise</t>
+          <t>Feature and order manipulations in a free recall task affect memory for current and future lists</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41598-022-17781-0</t>
+          <t>https://psyarxiv.com/erzfp</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>13822</v>
-      </c>
+          <t>PsyArXiv</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>doi.org/10.1038/s41598-022-17781-0</t>
+          <t>10.31234/osf.io/erzfp</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>https://trebuchet.public.springernature.app/get_content/36d8a20c-775b-49b5-a60e-2e7339f2a396</t>
+          <t>https://psyarxiv.com/erzfp</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/brainfit-paper</t>
+          <t>https://github.com/ContextLab/FRFR-analyses</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/brainfit-paper</t>
+          <t>https://github.com/ContextLab/FRFR-analyses</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Whitaker EC: none; Fitzpatrick PC: undergrad</t>
         </is>
       </c>
     </row>
     <row r="13" ht="68" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>brainiak.png</t>
+          <t>fitness-tracking.png</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Kumar M, Anderson MJ, Antony JW, Baldassano C, Brooks PP, Cai MB, Chen P-HC, Ellis CT, Henselman-Petrusek G, Huberdeau D, Hutchinson BJ, Li PY, Lu Q, Manning JR, Mennen AC, Nastase SA, Richard H, Schapiro AC, Schuck NW, Suo D, Turek JS, Vo VA, Wallace G, Wang Y, Zhang H, Zhu X, Capotă M, Cohen JD, Hasson U, Li K, Ramadge PJ, Turk-Browne NB, Willke TL, Norman KA</t>
+          <t>Manning JR, Notaro GM, Chen E, Fitzpatrick PC</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
@@ -1195,111 +1202,112 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>BrainIAK: The Brain Imaging Analysis Kit</t>
+          <t>Fitness tracking reveals task-specific associations between memory, mental health, and physical activity</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>https://apertureneuropub.cloud68.co/articles/42/index.html</t>
+          <t>https://doi.org/10.1038/s41598-022-17781-0</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Aperture</t>
+          <t>Scientific Reports</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>1—19</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n">
+        <v>13822</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>https://osf.io/db2ev/</t>
+          <t>https://trebuchet.public.springernature.app/get_content/36d8a20c-775b-49b5-a60e-2e7339f2a396</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/brainiak/brainiak-aperture</t>
+          <t>https://github.com/ContextLab/brainfit-paper</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/brainiak/brainiak-aperture</t>
+          <t>https://github.com/ContextLab/brainfit-paper</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Fitzpatrick PC: undergrad</t>
         </is>
       </c>
     </row>
     <row r="14" ht="51" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>timecorr.png</t>
+          <t>brainiak.png</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Owen LLW, Chang TH, Manning JR</t>
+          <t>Kumar M, Anderson MJ, Antony JW, Baldassano C, Brooks PP, Cai MB, Chen P-HC, Ellis CT, Henselman-Petrusek G, Huberdeau D, Hutchinson JB, Li YP, Lu Q, Manning JR, Mennen AC, Nastase SA, Richard H, Schapiro AC, Schuck NW, Shvartsman M, Sundaram N, Suo D, Turek JS, Turner D, Vo VA, Wallace G, Wang Y, Williams JA, Zhang H, Zhu X, Capotă M, Cohen JD, Hasson U, Li K, Ramadge PJ, Turk-Browne NB, Willke TL, Norman KA</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>High-level cognition during story listening is reflected in high-order dynamic correlations in neural activity patterns</t>
+          <t>BrainIAK: The Brain Imaging Analysis Kit</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41467-021-25876-x</t>
+          <t>https://apertureneuropub.cloud68.co/articles/42/index.html</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Nature Communications</t>
+          <t>Aperture</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>5728</v>
+        <v>4</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>doi.org/10.1101/763821</t>
+          <t>1—19</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>https://www.biorxiv.org/content/10.1101/763821v3</t>
+          <t>https://osf.io/db2ev/</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/timecorr-paper</t>
+          <t>https://github.com/brainiak/brainiak-aperture</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/timecorr-paper</t>
+          <t>https://github.com/brainiak/brainiak-aperture</t>
         </is>
       </c>
     </row>
     <row r="15" ht="51" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>ScangosEtAl20-01.png</t>
+          <t>timecorr.png</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Scangos KW, Khambhati AN, Daly PM, Owen LW, Manning JR, Ambrose JB, Austin E, Dawes HE, Krystal AD, Chang EF</t>
+          <t>Owen LLW, Chang TH, Manning JR</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
@@ -1307,53 +1315,51 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Biomarkers of depression symptoms defined by direct intracranial neurophysiology</t>
+          <t>High-level cognition during story listening is reflected in high-order dynamic correlations in neural activity patterns</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>https://www.frontiersin.org/articles/10.3389/fnhum.2021.746499/full</t>
+          <t>https://www.nature.com/articles/s41467-021-25876-x</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Frontiers in Human Neuroscience</t>
+          <t>Nature Communications</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>doi.org/10.3389/fnhum.2021.746499</t>
-        </is>
+      <c r="I15" s="3" t="n">
+        <v>5728</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>https://www.frontiersin.org/articles/10.3389/fnhum.2021.746499/full</t>
+          <t>https://www.biorxiv.org/content/10.1101/763821v3</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>https://supereeg.readthedocs.io/en/latest/</t>
+          <t>https://github.com/ContextLab/timecorr-paper</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>https://zenodo.org/record/5540172#.YXQQunkpDS5</t>
+          <t>https://github.com/ContextLab/timecorr-paper</t>
         </is>
       </c>
     </row>
     <row r="16" ht="68" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>rodent-hippocampus.png</t>
+          <t>ScangosEtAl20-01.png</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Chen H-T, Manning JR, van der Meer MAA</t>
+          <t>Scangos KW, Khambhati AN, Daly PM, Owen LLW, Manning JR, Ambrose JB, Austin E, Dawes HE, Krystal AD, Chang EF</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
@@ -1361,55 +1367,51 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Between-subject prediction reveals a shared representational geometry in the rodent hippocampus</t>
+          <t>Distributed subnetworks of depression defined by direct intracranial neurophysiology</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S0960982221010514</t>
+          <t>https://www.frontiersin.org/articles/10.3389/fnhum.2021.746499/full</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Current Biology</t>
+          <t>Frontiers in Human Neuroscience</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>4293—4304</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n">
+        <v>746499</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>https://authors.elsevier.com/c/1ddOZ3QW8RwpPI</t>
+          <t>https://www.frontiersin.org/articles/10.3389/fnhum.2021.746499/full</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/vandermeerlab/hc_hyperalign/tree/v1.0.0</t>
+          <t>https://supereeg.readthedocs.io/en/latest/</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/vandermeerlab/hc_hyperalign/tree/v1.0.0</t>
+          <t>https://zenodo.org/record/5540172#.YXQQunkpDS5</t>
         </is>
       </c>
     </row>
     <row r="17" ht="68" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>mental-time-travel.png</t>
+          <t>rodent-hippocampus.png</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Manning JR</t>
+          <t>Chen HT, Manning JR, van der Meer MAA</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
@@ -1417,55 +1419,60 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Episodic memory: mental time travel or a quantum 'memory wave' function?</t>
+          <t>Between-subject prediction reveals a shared representational geometry in the rodent hippocampus</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>https://psycnet.apa.org/record/2021-47824-001</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S0960982221010514</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Psychological Review</t>
+          <t>Current Biology</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>128</v>
+        <v>31</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>711—725</t>
+          <t>4293—4304.e5</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>https://psyarxiv.com/6zjwb</t>
+          <t>https://authors.elsevier.com/c/1ddOZ3QW8RwpPI</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/mental-time-travel-paper</t>
+          <t>https://github.com/vandermeerlab/hc_hyperalign/tree/v1.0.0</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>https://dataspace.princeton.edu/jspui/handle/88435/dsp01nz8062179</t>
+          <t>https://github.com/vandermeerlab/hc_hyperalign/tree/v1.0.0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Chen HT: grad</t>
         </is>
       </c>
     </row>
     <row r="18" ht="51" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>XieEtAl21-08.png</t>
+          <t>mental-time-travel.png</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Xie T, Cheong JH, Manning JR, Brandt AM, Aronson JP, Jobst BC, Bujarski KA, Chang LJ</t>
+          <t>Manning JR</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -1473,47 +1480,55 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Minimal functional alignment of ventromedial prefrontal cortex intracranial EEG signals during naturalistic viewing</t>
+          <t>Episodic memory: mental time travel or a quantum 'memory wave' function?</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>https://www.biorxiv.org/content/10.1101/2021.05.10.443308v1</t>
+          <t>https://psycnet.apa.org/record/2021-47824-001</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>bioRxiv</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="n"/>
-      <c r="H18" s="3" t="n"/>
+          <t>Psychological Review</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>2021.05.10.443308v1</t>
+          <t>711—725</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>https://www.biorxiv.org/content/10.1101/2021.05.10.443308v1</t>
+          <t>https://psyarxiv.com/6zjwb</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/cosanlab/naturalistic_iEEG_func_align</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="n"/>
+          <t>https://github.com/ContextLab/mental-time-travel-paper</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>https://dataspace.princeton.edu/jspui/handle/88435/dsp01nz8062179</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="68" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>vmPFC-dynamics.png</t>
+          <t>XieEtAl21-08.png</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Chang LJ, Jolly E, Cheong JH, Rapuano K, Greenstein N, Chen P-HA, Manning JR</t>
+          <t>Xie T, Cheong JH, Manning JR, Brandt AM, Aronson JP, Jobst BC, Bujarski KA, Chang LJ</t>
         </is>
       </c>
       <c r="C19" s="3" t="n">
@@ -1521,55 +1536,52 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Endogenous variation in ventromedial prefrontal cortex state dynamics during naturalistic viewing reflects affective experience</t>
+          <t>Minimal functional alignment of ventromedial prefrontal cortex intracranial EEG signals during naturalistic viewing</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>https://advances.sciencemag.org/content/7/17/eabf7129</t>
+          <t>https://www.biorxiv.org/content/10.1101/2021.05.10.443308v1</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Science Advances</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>17</v>
-      </c>
+          <t>bioRxiv</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>doi.org/10.1126/sciadv.abf7129</t>
+          <t>2021.05.10.443308v1</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>https://www.biorxiv.org/content/10.1101/487892v3</t>
+          <t>https://www.biorxiv.org/content/10.1101/2021.05.10.443308v1</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/cosanlab/vmPFC_dynamics</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/cosanlab/vmPFC_dynamics</t>
+          <t>https://github.com/cosanlab/naturalistic_iEEG_func_align</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="n"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Xie T: grad; Cheong JH: grad</t>
         </is>
       </c>
     </row>
     <row r="20" ht="51" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>false-familiarity.png</t>
+          <t>vmPFC-dynamics.png</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Ziman K, Manning JR</t>
+          <t>Chang LJ, Jolly E, Cheong JH, Rapuano KM, Greenstein N, Chen PHA, Manning JR</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -1577,51 +1589,60 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Unexpected false feelings of familiarity about faces are associated with increased pupil dilations</t>
+          <t>Endogenous variation in ventromedial prefrontal cortex state dynamics during naturalistic viewing reflects affective experience</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>https://www.biorxiv.org/content/10.1101/2021.02.22.432360v1</t>
+          <t>https://advances.sciencemag.org/content/7/17/eabf7129</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>bioRxiv</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
+          <t>Science Advances</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>17</v>
+      </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>10.1101/2021.02.22.432360v1</t>
+          <t>eabf7129</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>https://www.biorxiv.org/content/10.1101/2021.02.22.432360v1</t>
+          <t>https://www.biorxiv.org/content/10.1101/487892v3</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/attention-memory-task</t>
+          <t>https://github.com/cosanlab/vmPFC_dynamics</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/attention-memory-task</t>
+          <t>https://github.com/cosanlab/vmPFC_dynamics</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Jolly E: postdoc; Cheong JH: grad; Rapuano KM: grad; Greenstein N: undergrad; Chen PHA: postdoc</t>
         </is>
       </c>
     </row>
     <row r="21" ht="51" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Sherlock-40.png</t>
+          <t>false-familiarity.png</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Heusser AC, Fitzpatrick PC, Manning JR</t>
+          <t>Ziman K, Manning JR</t>
         </is>
       </c>
       <c r="C21" s="3" t="n">
@@ -1629,211 +1650,216 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Geometric models reveal behavioral and neural signatures of transforming naturalistic experiences into episodic memories</t>
+          <t>Unexpected false feelings of familiarity about faces are associated with increased pupil dilations</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>https://rdcu.be/cpMwZ</t>
+          <t>https://www.biorxiv.org/content/10.1101/2021.02.22.432360v1</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Nature Human Behaviour</t>
+          <t>bioRxiv</t>
         </is>
       </c>
       <c r="G21" s="3" t="n"/>
       <c r="H21" s="3" t="n"/>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41562-021-01051-6</t>
+          <t>10.1101/2021.02.22.432360v1</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>https://rdcu.be/cpMwZ</t>
+          <t>https://www.biorxiv.org/content/10.1101/2021.02.22.432360v1</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/sherlock-topic-model-paper</t>
+          <t>https://github.com/ContextLab/attention-memory-task</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>https://dataspace.princeton.edu/jspui/handle/88435/dsp01nz8062179</t>
+          <t>https://github.com/ContextLab/attention-memory-task</t>
         </is>
       </c>
     </row>
     <row r="22" ht="51" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>supereeg-gp.png</t>
+          <t>Sherlock-40.png</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Owen LLW, Muntianu TA, Heusser AC, Daly P, Scangos KW, Manning JR</t>
+          <t>Heusser AC, Fitzpatrick PC, Manning JR</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>A Gaussian process model of human electrocorticographic data</t>
+          <t>Geometric models reveal behavioural and neural signatures of transforming experiences into memories</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/cercor/article/30/10/5333/5851264</t>
+          <t>https://rdcu.be/cpMwZ</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Cerebral Cortex</t>
+          <t>Nature Human Behaviour</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>5333—5345</t>
+          <t>905—919</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>https://academic.oup.com/cercor/article/30/10/5333/5851264</t>
+          <t>https://rdcu.be/cpMwZ</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/supereeg_paper</t>
+          <t>https://github.com/ContextLab/sherlock-topic-model-paper</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>http://memory.psych.upenn.edu/Request_EEG_access?paper=EzzyEtal17</t>
+          <t>https://dataspace.princeton.edu/jspui/handle/88435/dsp01nz8062179</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Fitzpatrick PC: undergrad</t>
         </is>
       </c>
     </row>
     <row r="23" ht="51" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>hypertools.png</t>
+          <t>supereeg-gp.png</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Heusser AC, Ziman K, Owen LW, Manning JR</t>
+          <t>Owen LLW, Muntianu TA, Heusser AC, Daly PM, Scangos KW, Manning JR</t>
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>HyperTools: A Python toolbox for gaining geometric insights into high-dimensional data</t>
+          <t>A Gaussian process model of human electrocorticographic data</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>http://jmlr.org/papers/v18/17-434.html</t>
+          <t>https://academic.oup.com/cercor/article/30/10/5333/5851264</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Journal of Machine Learning Research</t>
+          <t>Cerebral Cortex</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>152</v>
+        <v>10</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>1—6</t>
+          <t>5333—5345</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>http://jmlr.org/papers/volume18/17-434/17-434.pdf</t>
+          <t>https://academic.oup.com/cercor/article/30/10/5333/5851264</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/hypertools</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="n"/>
+          <t>https://github.com/ContextLab/supereeg_paper</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>http://memory.psych.upenn.edu/Request_EEG_access?paper=EzzyEtal17</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="68" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Sherlock-41.png</t>
+          <t>naturalistic-data.png</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Heusser AC, Manning JR</t>
+          <t>Chang L, Manning JR, Baldassano C, de la Vega A, Fleetwood G, Geerligs L, Haxby J, Lahnakoski J, Parkinson C, Shappell H, Shim WM, Wager T, Yarkoni T, Yeshurun Y, Finn E</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Capturing the geometric structure of episodic memories for naturalistic experiences</t>
+          <t>Naturalistic data analysis</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>https://ccneuro.org/2018/proceedings/1267.pdf</t>
+          <t>https://naturalistic-data.org/</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Conference on Cognitive Computational Neuroscience</t>
+          <t>Zenodo</t>
         </is>
       </c>
       <c r="G24" s="3" t="n"/>
       <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>PS-2B.16</t>
+          <t>10.5281/zenodo.3937849</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>https://ccneuro.org/2018/proceedings/1267.pdf</t>
+          <t>https://naturalistic-data.org/</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/sherlock-topic-model-paper</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>https://dataspace.princeton.edu/jspui/handle/88435/dsp01nz8062179</t>
-        </is>
-      </c>
+          <t>https://github.com/naturalistic-data-analysis/naturalistic_data_analysis</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="n"/>
     </row>
     <row r="25" ht="51" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>SketchLogo_AutoFR-22.png</t>
+          <t>hypertools.png</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Ziman K, Heusser AC, Fitzpatrick PC, Field CE, Manning JR</t>
+          <t>Heusser AC, Ziman K, Owen LLW, Manning JR</t>
         </is>
       </c>
       <c r="C25" s="3" t="n">
@@ -1841,53 +1867,51 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Is automatic speech-to-text transcription ready for use in psychological experiments?</t>
+          <t>HyperTools: A Python toolbox for gaining geometric insights into high-dimensional data</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>https://link.springer.com/article/10.3758/s13428-018-1037-4</t>
+          <t>http://jmlr.org/papers/v18/17-434.html</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Behavior Research Methods</t>
+          <t>Journal of Machine Learning Research</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="H25" s="3" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>152</v>
+      </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>2597—2605</t>
+          <t>1—6</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>https://psyarxiv.com/psh48</t>
+          <t>http://jmlr.org/papers/volume18/17-434/17-434.pdf</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/autoFR</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/ContextLab/quail/tree/master/quail/data</t>
-        </is>
-      </c>
+          <t>https://github.com/ContextLab/hypertools</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="n"/>
     </row>
     <row r="26" ht="51" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>htfa-connectivity.png</t>
+          <t>Sherlock-41.png</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Manning JR, Zhu X, Willke T, Ranganath R, Stachenfeld K, Hasson U, Blei DM, Norman KA</t>
+          <t>Heusser AC, Manning JR</t>
         </is>
       </c>
       <c r="C26" s="3" t="n">
@@ -1895,36 +1919,34 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>A probabilistic approach to discovering dynamic full-brain functional connectivity patterns</t>
+          <t>Capturing the geometric structure of episodic memories for naturalistic experiences</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S1053811918300715?via%3Dihub</t>
+          <t>https://ccneuro.org/2018/proceedings/1267.pdf</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>NeuroImage</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>180</v>
-      </c>
+          <t>Conference on Cognitive Computational Neuroscience</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n"/>
       <c r="H26" s="3" t="n"/>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>243—252</t>
+          <t>PS-2B.16</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/pii/S1053811918300715?via%3Dihub</t>
+          <t>https://ccneuro.org/2018/proceedings/1267.pdf</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/IntelPNI/brainiak</t>
+          <t>https://github.com/ContextLab/sherlock-topic-model-paper</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -1936,94 +1958,100 @@
     <row r="27" ht="51" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>quail.png</t>
+          <t>SketchLogo_AutoFR-22.png</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Heusser AC, Fitzpatrick PC, Field CE, Ziman K, Manning JR</t>
+          <t>Ziman K, Heusser AC, Fitzpatrick PC, Field CE, Manning JR</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Quail: A Python toolbox for analyzing and plotting free recall data</t>
+          <t>Is automatic speech-to-text transcription ready for use in psychological experiments?</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>http://joss.theoj.org/papers/10.21105/joss.00424</t>
+          <t>https://link.springer.com/article/10.3758/s13428-018-1037-4</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>The Journal of Open Source Software</t>
+          <t>Behavior Research Methods</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>2597—2605</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/openjournals/joss-papers/raw/master/joss.00424/10.21105.joss.00424.pdf</t>
+          <t>https://psyarxiv.com/psh48</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>http://cdl-quail.readthedocs.io/en/latest/</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="n"/>
+          <t>https://github.com/ContextLab/autoFR</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/ContextLab/quail/tree/master/quail/data</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="51" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>AndeEtAl16-16.png</t>
+          <t>htfa-connectivity.png</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Anderson MJ, Capota M, Turek JS, Zhu X, Wilke TL, Chen PH, Manning JR, Ramadge PJ, Norman KA</t>
+          <t>Manning JR, Zhu X, Willke TL, Ranganath R, Stachenfeld K, Hasson U, Blei DM, Norman KA</t>
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Enabling factor analysis on thousand-subject neuroimaging datasets</t>
+          <t>A probabilistic approach to discovering dynamic full-brain functional connectivity patterns</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>https://ieeexplore.ieee.org/document/7840719/</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S1053811918300715?via%3Dihub</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>IEEE International Conference on Big Data (Big Data)</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="n"/>
+          <t>NeuroImage</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>180</v>
+      </c>
       <c r="H28" s="3" t="n"/>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>1151—1160</t>
+          <t>243—252</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>http://arxiv.org/pdf/1608.04647.pdf</t>
+          <t>https://www.sciencedirect.com/science/article/pii/S1053811918300715?via%3Dihub</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -2031,169 +2059,186 @@
           <t>https://github.com/IntelPNI/brainiak</t>
         </is>
       </c>
-      <c r="L28" s="3" t="n"/>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>https://dataspace.princeton.edu/jspui/handle/88435/dsp01nz8062179</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Ranganath R: grad; Stachenfeld K: grad</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="68" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>intentional-forgetting.png</t>
+          <t>quail.png</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Manning JR, Hulbert JC, Williams J, Piloto L, Sahakyan L, Norman KA</t>
+          <t>Heusser AC, Fitzpatrick PC, Field CE, Ziman K, Manning JR</t>
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>A neural signature of contextually mediated intentional forgetting</t>
+          <t>Quail: A Python toolbox for analyzing and plotting free recall data</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>http://link.springer.com/content/pdf/10.3758%2Fs13423-016-1024-7.pdf</t>
+          <t>http://joss.theoj.org/papers/10.21105/joss.00424</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Psychonomic Bulletin and Review</t>
+          <t>The Journal of Open Source Software</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>1534—1542</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>424</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>http://link.springer.com/content/pdf/10.3758%2Fs13423-016-1024-7.pdf</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>https://openneuro.org/datasets/ds001745/versions/1.0.0</t>
-        </is>
-      </c>
+          <t>https://github.com/openjournals/joss-papers/raw/master/joss.00424/10.21105.joss.00424.pdf</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>http://cdl-quail.readthedocs.io/en/latest/</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="n"/>
     </row>
     <row r="30" ht="51" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>BensEtAl14-14.png</t>
+          <t>AndeEtAl16-16.png</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Benson NC, Manning JR, Brainard DH</t>
+          <t>Anderson MJ, Capota M, Turek JS, Zhu X, Willke TL, Wang Y, Chen P-H, Manning JR, Ramadge PJ, Norman KA</t>
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Unsupervised learning of cone spectral classes from natural images</t>
+          <t>Enabling factor analysis on thousand-subject neuroimaging datasets</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/BensEtal14.pdf</t>
+          <t>https://ieeexplore.ieee.org/document/7840719/</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>PLoS Computational Biology</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>6</v>
-      </c>
+          <t>IEEE International Conference on Big Data (Big Data)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>e1003652</t>
+          <t>1151—1160</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/BensEtal14.pdf</t>
+          <t>http://arxiv.org/pdf/1608.04647.pdf</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/DavidBrainard/ReceptorLearning</t>
+          <t>https://github.com/IntelPNI/brainiak</t>
         </is>
       </c>
       <c r="L30" s="3" t="n"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Chen P-H: grad</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="51" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>MannEtAl14b-13.png</t>
+          <t>intentional-forgetting.png</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Manning JR, Ranganath R, Keung W, Turk-Browne NB, Cohen JD, Norman KA, Blei DM</t>
+          <t>Manning JR, Hulbert JC, Williams J, Piloto L, Sahakyan L, Norman KA</t>
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Hierarchical Topographic Factor Analysis</t>
+          <t>A neural signature of contextually mediated intentional forgetting</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal14b.pdf</t>
+          <t>http://link.springer.com/content/pdf/10.3758%2Fs13423-016-1024-7.pdf</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>IEEE International Workshop on Pattern Recognition in Neuroimaging</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
+          <t>Psychonomic Bulletin and Review</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>113—116</t>
+          <t>1534—1542</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal14b.pdf</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>https://github.com/IntelPNI/brainiak</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="n"/>
+          <t>http://link.springer.com/content/pdf/10.3758%2Fs13423-016-1024-7.pdf</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n"/>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>https://openneuro.org/datasets/ds001745/versions/1.0.0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Piloto L: grad</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="85" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>MannEtAl14c-12.png</t>
+          <t>BensEtAl14-14.png</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Manning JR, Ranganath R, Norman KA, Blei DA</t>
+          <t>Benson NC, Manning JR, Brainard DH</t>
         </is>
       </c>
       <c r="C32" s="3" t="n">
@@ -2201,38 +2246,38 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Topographic Factor Analysis: a Bayesian model for inferring brain networks from neural data</t>
+          <t>Unsupervised learning of cone spectral classes from natural images</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal14c.pdf</t>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/BensEtal14.pdf</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>PLoS One</t>
+          <t>PLoS Computational Biology</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>e94914</t>
+          <t>e1003652</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal14c.pdf</t>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/BensEtal14.pdf</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/IntelPNI/brainiak</t>
+          <t>https://github.com/DavidBrainard/ReceptorLearning</t>
         </is>
       </c>
       <c r="L32" s="3" t="n"/>
@@ -2240,96 +2285,94 @@
     <row r="33" ht="68" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>MannEtAl14a-11.png</t>
+          <t>MannEtAl14b-13.png</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Manning JR, Lew TF, Li N, Kahana MJ, Sekuler RW</t>
+          <t>Manning JR, Ranganath R, Keung W, Turk-Browne NB, Cohen JD, Norman KA, Blei DM</t>
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>MAGELLAN: a cognitive map-based model of human wayfinding</t>
+          <t>Hierarchical Topographic Factor Analysis</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal14a.pdf</t>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal14b.pdf</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Journal of Experimental Psychology: General</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>143</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>3</v>
-      </c>
+          <t>IEEE International Workshop on Pattern Recognition in Neuroimaging</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>1314—1330</t>
+          <t>1—4</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal14a.pdf</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>http://memory.psych.upenn.edu/files/pubs/MannEtal14a.data.tgz</t>
-        </is>
-      </c>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal14b.pdf</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/IntelPNI/brainiak</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="n"/>
     </row>
     <row r="34" ht="51" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>MannEtAl12b-10.png</t>
+          <t>MannEtAl14c-12.png</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Manning JR, Gershman SJ, Norman KA, Blei DM</t>
+          <t>Manning JR, Ranganath R, Norman KA, Blei DM</t>
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Factor topographic latent source analysis: factor analysis for brain images</t>
+          <t>Topographic Factor Analysis: a Bayesian model for inferring brain networks from neural data</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal12b.pdf</t>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal14c.pdf</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Proceedings of the NIPS Workshop on Machine Learning and Interpretation in Neuroimaging</t>
+          <t>PLoS One</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" s="3" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>e94914</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal12b.pdf</t>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal14c.pdf</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -2342,60 +2385,64 @@
     <row r="35" ht="68" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>MannEtAl12a-09.png</t>
+          <t>MannEtAl14a-11.png</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Manning JR, Sperling MR, Sharan A, Rosenberg EA, Kahana MJ</t>
+          <t>Manning JR, Lew TF, Li N, Sekuler R, Kahana MJ</t>
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Spontaneously reactivated patterns in frontal and temporal lobe predict semantic clustering during memory search</t>
+          <t>MAGELLAN: a cognitive map-based model of human wayfinding</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal12a.pdf</t>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal14a.pdf</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>The Journal of Neuroscience</t>
+          <t>Journal of Experimental Psychology: General</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>32</v>
+        <v>143</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>8800—8816</t>
+          <t>1314—1330</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal12a.pdf</t>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal14a.pdf</t>
         </is>
       </c>
       <c r="K35" s="3" t="n"/>
-      <c r="L35" s="3" t="n"/>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>http://memory.psych.upenn.edu/files/pubs/MannEtal14a.data.tgz</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="51" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>MannKaha12-08.png</t>
+          <t>MannEtAl12b-10.png</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Manning JR, Kahana MJ</t>
+          <t>Manning JR, Gershman SJ, Norman KA, Blei DM</t>
         </is>
       </c>
       <c r="C36" s="3" t="n">
@@ -2403,81 +2450,83 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Interpreting semantic clustering effects in free recall</t>
+          <t>Factor topographic latent source analysis: factor analysis for brain images</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannKaha12.pdf</t>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal12b.pdf</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Memory</t>
+          <t>Proceedings of the NIPS Workshop on Machine Learning and Interpretation in Neuroimaging</t>
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H36" s="3" t="n"/>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>511—517</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannKaha12.pdf</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="n"/>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal12b.pdf</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/IntelPNI/brainiak</t>
+        </is>
+      </c>
       <c r="L36" s="3" t="n"/>
     </row>
     <row r="37" ht="68" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MannEtAl11-02.png</t>
+          <t>MannEtAl12a-09.png</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Manning JR, Polyn SM, Baltuch G, Litt B, Kahana MJ</t>
+          <t>Manning JR, Sperling MR, Sharan A, Rosenberg EA, Kahana MJ</t>
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Oscillatory patterns in temporal lobe reveal context reinstatement during memory search</t>
+          <t>Spontaneously reactivated patterns in frontal and temporal lobe predict semantic clustering during memory search</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal11.pdf</t>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal12a.pdf</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Proceedings of the National Academy of Sciences of the United States of America</t>
+          <t>The Journal of Neuroscience</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>12893—12897</t>
+          <t>8871—8878</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal11.pdf</t>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal12a.pdf</t>
         </is>
       </c>
       <c r="K37" s="3" t="n"/>
@@ -2486,44 +2535,46 @@
     <row r="38" ht="51" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>JacoEtAl10b-07.png</t>
+          <t>MannKaha12-08.png</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Jacobs J, Manning JR, Kahana MJ</t>
+          <t>Manning JR, Kahana MJ</t>
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Response to Miller: "Broadband" vs. "high gamma" electrocorticographic signals</t>
+          <t>Interpreting semantic clustering effects in free recall</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/JacoEtal10b.pdf</t>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannKaha12.pdf</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>The Journal of Neuroscience</t>
+          <t>Memory</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="H38" s="3" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>511—517</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/JacoEtal10b.pdf</t>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannKaha12.pdf</t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
@@ -2532,46 +2583,46 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MannEtAl09-05.png</t>
+          <t>MannEtAl11-02.png</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Manning JR, Jacobs J, Fried I, Kahana MJ</t>
+          <t>Manning JR, Polyn SM, Baltuch G, Litt B, Kahana MJ</t>
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Broadband shifts in local field potential power spectra are correlated with single-neuron spiking in humans</t>
+          <t>Oscillatory patterns in temporal lobe reveal context reinstatement during memory search</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal09.pdf</t>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal11.pdf</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>The Journal of Neuroscience</t>
+          <t>Proceedings of the National Academy of Sciences of the United States of America</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>13613—13620</t>
+          <t>12893—12897</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal09.pdf</t>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal11.pdf</t>
         </is>
       </c>
       <c r="K39" s="3" t="n"/>
@@ -2580,48 +2631,144 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>MannBrai09-06.png</t>
+          <t>JacoEtAl10b-07.png</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Manning JR, Brainard DB</t>
+          <t>Jacobs J, Manning JR, Kahana MJ</t>
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Optimal design of photoreceptor mosaics: why we do not see color at night</t>
+          <t>Response to Miller: "Broadband" vs. "high gamma" electrocorticographic signals</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannBrai09.pdf</t>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/JacoEtal10b.pdf</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Visual Neuroscience</t>
+          <t>The Journal of Neuroscience</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H40" s="3" t="n"/>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>5—19</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannBrai09.pdf</t>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/JacoEtal10b.pdf</t>
         </is>
       </c>
       <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>MannEtAl09-05.png</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Manning JR, Jacobs J, Fried I, Kahana MJ</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Broadband shifts in local field potential power spectra are correlated with single-neuron spiking in humans</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal09.pdf</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>The Journal of Neuroscience</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>13613—13620</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal09.pdf</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="n"/>
+      <c r="L41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>MannBrai09-06.png</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Manning JR, Brainard DH</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>2009</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Optimal design of photoreceptor mosaics: why we do not see color at night</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannBrai09.pdf</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Visual Neuroscience</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>5—19</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannBrai09.pdf</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="n"/>
+      <c r="L42" s="3" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2637,7 +2784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2703,6 +2850,26 @@
           <t>pdf_link</t>
         </is>
       </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>pages</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>author_roles</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>cv_note</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
@@ -2715,14 +2882,12 @@
           <t>Manning JR</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+      <c r="C2" s="6" t="n">
+        <v>2023</v>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>Identifying stimulus-driven neural activity patterns in multi-patient intracranial recordings</t>
+          <t>How can I identify stimulus-driven neural activity patterns in multi-patient ECoG data?</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -2737,12 +2902,12 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>Intracranial EEG for Cognitive Neuroscience</t>
+          <t>Intracranial EEG: A Guide for Cognitive Neuroscientists</t>
         </is>
       </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>New York, NY</t>
+          <t>Cham, Switzerland</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
@@ -2754,6 +2919,14 @@
         <is>
           <t>https://arxiv.org/pdf/2202.01933.pdf</t>
         </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>803—836</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
@@ -2767,10 +2940,8 @@
           <t>Manning JR</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="C3" s="6" t="n">
+        <v>2024</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
@@ -2789,12 +2960,12 @@
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>Handbook of Human Memory: Foundations and Applications</t>
+          <t>The Oxford Handbook of Human Memory</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
         <is>
-          <t>Oxford, UK</t>
+          <t>New York, NY</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
@@ -2806,6 +2977,14 @@
         <is>
           <t>https://psyarxiv.com/g2w73/download</t>
         </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1114—1139</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1">
@@ -2816,13 +2995,11 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Manning JR, Norman KA, Kahana MJ</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
+          <t>Manning JR, Kahana MJ, Norman KA</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>2014</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
@@ -2836,12 +3013,12 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Gazzaniga M</t>
+          <t>Gazzaniga MS, Mangun GR</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>The Cognitive Neurosciences, 5th Edition</t>
+          <t>The Cognitive Neurosciences, Fifth Edition</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -2858,6 +3035,9 @@
         <is>
           <t>http://caligari.dartmouth.edu/~jmanning/pubs/MannEtal15.pdf</t>
         </is>
+      </c>
+      <c r="L4" t="n">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -3973,7 +3973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -4067,192 +4067,166 @@
     <row r="4" ht="51" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>naturalistic-data.png</t>
+          <t>programming-psych.png</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Naturalistic Data Analysis</t>
+          <t>Introduction to Programming for Psychological Scientists</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>https://naturalistic-data.org/content/intro.html</t>
+          <t>https://github.com/ContextLab/cs-for-psych</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>An online book that includes a collection of state-of-the-art approaches to analyzing naturalistic data.</t>
+          <t>A self-directed open course intended to introduce students to fundamental computational tools used by modern psychological researchers.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>https://github.com/naturalistic-data-analysis/naturalistic_data_analysis</t>
+          <t>https://github.com/ContextLab/cs-for-psych</t>
         </is>
       </c>
     </row>
     <row r="5" ht="68" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>programming-psych.png</t>
+          <t>lab-tutorials.png</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Introduction to Programming for Psychological Scientists</t>
+          <t>Lab tutorials</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/cs-for-psych</t>
+          <t>https://github.com/ContextLab/CDL-tutorials</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>A self-directed open course intended to introduce students to fundamental computational tools used by modern psychological researchers.</t>
+          <t>A collection of lab tutorials on a range of quantitative and computational topics.</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/cs-for-psych</t>
+          <t>https://github.com/ContextLab/CDL-tutorials</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>lab-tutorials.png</t>
+          <t>mind-summer.png</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Lab tutorials</t>
+          <t>Methods in Neuroscience at Dartmouth (MIND)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/CDL-tutorials</t>
+          <t>http://mindsummerschool.org/</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>A collection of lab tutorials on a range of quantitative and computational topics.</t>
+          <t>A 10-day intensive summer course on cutting-edge computational methods.</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/CDL-tutorials</t>
+          <t>https://github.com/Summer-MIND</t>
         </is>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>mind-summer.png</t>
+          <t>StorytellingWithData-23.webp</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Methods in Neuroscience at Dartmouth (MIND)</t>
+          <t>Storytelling with Data</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>http://mindsummerschool.org/</t>
+          <t>https://github.com/ContextLab/storytelling-with-data</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>A 10-day intensive summer course on cutting-edge computational methods.</t>
+          <t>Data science course aimed at a general audience (no pre-requisites).</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>https://github.com/Summer-MIND</t>
+          <t>https://github.com/ContextLab/storytelling-with-data</t>
         </is>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>StorytellingWithData-23.webp</t>
+          <t>MechanicalBrain_Edited.webp</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Storytelling with Data</t>
+          <t>Computational Neuroscience</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/storytelling-with-data</t>
+          <t>https://github.com/ContextLab/computational-neuroscience</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Data science course aimed at a general audience (no pre-requisites).</t>
+          <t>A short University of Pennsylvania summer course that provides an introduction to programming in MATLAB, single-neuron models, ion channel models, basic neural networks, and neural decoding.</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>https://github.com/ContextLab/storytelling-with-data</t>
+          <t>https://github.com/ContextLab/computational-neuroscience</t>
         </is>
       </c>
     </row>
     <row r="9" ht="85" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>MechanicalBrain_Edited.webp</t>
+          <t>llm_course.jpg</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Computational Neuroscience</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/ContextLab/computational-neuroscience</t>
+          <t>Models of Language and Communication</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://context-lab.com/llm-course</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>A short University of Pennsylvania summer course that provides an introduction to programming in MATLAB, single-neuron models, ion channel models, basic neural networks, and neural decoding.</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>https://github.com/ContextLab/computational-neuroscience</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>llm_course.jpg</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Models of Language and Communication</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://context-lab.com/llm-course</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
           <t>An open course on language models, chatbots, and natural language processing</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>https://github.com/ContextLab/llm-course</t>
         </is>
       </c>
     </row>
+    <row r="10" ht="17" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
